--- a/PMI/Sinops/phase2-detail-design/DD/Sinops_IFレイアウト_発注勧告翌日以降.xlsx
+++ b/PMI/Sinops/phase2-detail-design/DD/Sinops_IFレイアウト_発注勧告翌日以降.xlsx
@@ -1362,6 +1362,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1665,7 +1668,11 @@
           <t>レビュー者</t>
         </is>
       </c>
-      <c r="C10" s="32" t="inlineStr"/>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>岩瀬、波多野</t>
+        </is>
+      </c>
       <c r="D10" s="58" t="n"/>
       <c r="E10" s="58" t="n"/>
       <c r="F10" s="59" t="n"/>
@@ -1676,7 +1683,11 @@
           <t>承認者</t>
         </is>
       </c>
-      <c r="C11" s="32" t="inlineStr"/>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>岩瀬</t>
+        </is>
+      </c>
       <c r="D11" s="58" t="n"/>
       <c r="E11" s="58" t="n"/>
       <c r="F11" s="59" t="n"/>
@@ -2005,27 +2016,33 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
+      <c r="B28" s="165" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="C28" s="166" t="n">
+        <v>46311</v>
+      </c>
+      <c r="D28" s="165" t="inlineStr">
+        <is>
+          <t>臧鵬仕</t>
+        </is>
+      </c>
+      <c r="E28" s="165" t="inlineStr">
+        <is>
+          <t>西友GCS上は gz。完了印は空の機能名.end。自動発注GCSは gz ではない</t>
+        </is>
+      </c>
       <c r="F28" s="10" t="n"/>
       <c r="G28" s="10" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1"/>
     <row r="30" ht="42" customHeight="1">
-      <c r="B30" s="165" t="inlineStr">
-        <is>
-          <t>※ 版数は 初版1.0、レビュー反映ごとに 1.1、1.2 と採番します。仕様変更による改訂は 2.0 として、変更管理表（D-5）に記録してください。</t>
-        </is>
-      </c>
+      <c r="B30" s="165" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="165" t="inlineStr">
-        <is>
-          <t>※ 未確定事項は空欄にせず、「09_確認事項・前提」シートに起票のうえ、該当箇所に「TBD-01」等の識別子を記載してください。</t>
-        </is>
-      </c>
+      <c r="B31" s="165" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2077,7 +2094,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="B2" s="173" t="inlineStr">
         <is>
-          <t>連携ファイルの物理仕様。送信・受信の双方向がある場合は本シートを複製してください</t>
+          <t>連携ファイルの物理仕様</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2153,7 @@
       <c r="C7" s="185" t="n"/>
       <c r="D7" s="172" t="inlineStr">
         <is>
-          <t>OUT物理: SIREJAN_RCMDORDER_LAST_YYYYMMDDhhmmss。IN論理: subkankoku.txt → IN物理: subkankoku_YYYYMMDDhhmmss.txt。24と混同しない</t>
+          <t>OUT物理: SIREJAN_RCMDORDER_LAST_YYYYMMDDhhmmss。IN論理: subkankoku.txt → IN物理: subkankoku_YYYYMMDDhhmmss.gz。24と混同しない</t>
         </is>
       </c>
       <c r="E7" s="184" t="n"/>
@@ -2248,7 +2265,7 @@
       <c r="C14" s="185" t="n"/>
       <c r="D14" s="172" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>西友GCSは gz＋空の機能名.end。自動発注GCSは gz ではない</t>
         </is>
       </c>
       <c r="E14" s="184" t="n"/>
@@ -3004,7 +3021,7 @@
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="173" t="inlineStr">
         <is>
-          <t>※ 項目Noはファイル内の並び順です。05_項目マッピングのNoとは一致しない場合があります。</t>
+          <t>※ 項目Noはファイル内の並び順。05 の No とは一致しない場合あり</t>
         </is>
       </c>
       <c r="C56" s="173" t="inlineStr">
@@ -3021,7 +3038,7 @@
     <row r="57" ht="30" customHeight="1">
       <c r="B57" s="173" t="inlineStr">
         <is>
-          <t>※ 桁数・型は受信側システムの制約を優先します。送信側で桁があふれる場合は 09_確認事項 へ起票してください。</t>
+          <t>※ 桁・型は受信側の制約を優先。桁あふれは 09 へ起票</t>
         </is>
       </c>
       <c r="C57" s="173" t="inlineStr">
@@ -4133,7 +4150,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="B2" s="173" t="inlineStr">
         <is>
-          <t>本IF固有のエラー処理を記載します。全体共通の方針は A-7 を参照してください</t>
+          <t>本IF固有。共通方針は A-7</t>
         </is>
       </c>
     </row>
@@ -4283,7 +4300,7 @@
       </c>
       <c r="H8" s="172" t="inlineStr">
         <is>
-          <t>切捨ては禁止</t>
+          <t>切捨てなし</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4434,7 @@
       </c>
       <c r="F12" s="148" t="inlineStr">
         <is>
-          <t>当該レコード扱い TBD-17。01/02/03 以外を 0/1 に黙って落とさない</t>
+          <t>当該レコード扱い TBD-17。01/02/03 以外は 0/1 にしない</t>
         </is>
       </c>
       <c r="G12" s="148" t="inlineStr">
@@ -4619,7 +4636,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="B2" s="173" t="inlineStr">
         <is>
-          <t>設計中に発生した未確定事項をここに集約します。全件クローズが詳細設計完了の条件です</t>
+          <t>未確定事項。全件クローズが詳細設計完了条件</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4727,7 @@
       </c>
       <c r="I6" s="172" t="inlineStr">
         <is>
-          <t>方針：西友（Sinops）とTRIALのマスタ統合により店舗の紐付けは解決する。本IFは独自の店CD変換・切捨てを持たない。出力桁は統合作業後のコード体系に従う</t>
+          <t>店CDはマスタ統合後のコード。6→4 の独自切捨てなし。桁は統合後</t>
         </is>
       </c>
       <c r="J6" s="172" t="inlineStr">
@@ -4785,7 +4802,7 @@
       </c>
       <c r="F8" s="148" t="inlineStr">
         <is>
-          <t>末松さん／運用</t>
+          <t>岩瀬・波多野／運用</t>
         </is>
       </c>
       <c r="G8" s="148" t="inlineStr">
@@ -4843,7 +4860,7 @@
       </c>
       <c r="I9" s="148" t="inlineStr">
         <is>
-          <t>GCS上は必ず末尾 _YYYYMMDDhhmmss。連携用: kankoku_YYYYMMDDhhmmss.txt / subkankoku_YYYYMMDDhhmmss.txt。自動発注: SIREJAN_RCMDORDER_LAST_YYYYMMDDhhmmss（拡張子は自動発注契約に従う）。DD-00 2026-09-21</t>
+          <t>西友GCSは gz（末尾 _YYYYMMDDhhmmss）。連携用: kankoku_YYYYMMDDhhmmss.gz / subkankoku_YYYYMMDDhhmmss.gz。完了印は空の kankoku.end / subkankoku.end。自動発注: SIREJAN_RCMDORDER_LAST_YYYYMMDDhhmmss（gz ではない）</t>
         </is>
       </c>
       <c r="J9" s="148" t="inlineStr">
@@ -4875,7 +4892,7 @@
       </c>
       <c r="F10" s="148" t="inlineStr">
         <is>
-          <t>末松さん／台帳</t>
+          <t>松尾</t>
         </is>
       </c>
       <c r="G10" s="148" t="inlineStr">
@@ -5019,7 +5036,7 @@
       </c>
       <c r="I13" s="148" t="inlineStr">
         <is>
-          <t>方針：仕入先マスタもマスタ統合で紐付けが解決する。本IFは独自のベンダーCD切捨て・変換を持たない。出力は統合作業後のコード体系に従う</t>
+          <t>仕入先はマスタ統合後のコード。9→8 の独自切捨てなし。桁は統合後</t>
         </is>
       </c>
       <c r="J13" s="148" t="inlineStr">
@@ -5156,7 +5173,7 @@
       </c>
       <c r="I16" s="148" t="inlineStr">
         <is>
-          <t>方針：マスタ統合により商品の紐付けは解決する。本IFは独自の仕入JAN変換を持たない。SireJANは統合後の商品コードを載せる</t>
+          <t>SireJAN は統合後の商品コード。独自変換なし</t>
         </is>
       </c>
       <c r="J16" s="148" t="inlineStr">
@@ -5246,7 +5263,7 @@
       </c>
       <c r="I18" s="148" t="inlineStr">
         <is>
-          <t>確定：Layer① は共通 1 本。STEP20 で当日／昨日の翌日以降を判定し 1 本採用。Layer③ は kankoku_* と subkankoku_*（末尾タイムスタンプ）を毎日出す。締切時刻は TBD-19</t>
+          <t>Layer① は 24/25 共通 1 ジョブ。STEP20 で 1 本採用。Layer③ は kankoku_* と subkankoku_* を毎日出力。締切は TBD-19</t>
         </is>
       </c>
       <c r="J18" s="148" t="inlineStr">
@@ -5588,14 +5605,14 @@
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="173" t="inlineStr">
         <is>
-          <t>※ 起票したTBDは、必ず課題管理表（D-3）にも登録し、番号を相互に記載してください。</t>
+          <t>※ TBD は課題管理表（D-3）にも登録。番号は相互に記載</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="173" t="inlineStr">
         <is>
-          <t>※ 期限は、前提クリア管理表（D-4）のゲート期限（9/30・10/16）と整合させてください。</t>
+          <t>※ 期限は前提クリア管理表（D-4）のゲート（9/30・10/16）に合わせる</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5764,7 @@
       </c>
       <c r="B42" s="173" t="inlineStr">
         <is>
-          <t>自動発注転送〜OrdreSV のServer／IP（範囲外だが経路明示用）</t>
+          <t>自動発注転送〜OrdreSV の Server／IP（本IFの外）</t>
         </is>
       </c>
       <c r="C42" s="173" t="inlineStr">
@@ -5807,7 +5824,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="B2" s="165" t="inlineStr">
         <is>
-          <t>Layer③ は当日・翌日以降を毎日出す。Layer① は 24/25 共通 1 ジョブで採用を判定する：当日が指定時刻までに作成済なら当日、障害または未作成なら昨日の翌日以降。発注IFへは 1 本だけ。</t>
+          <t>Layer③ は当日・翌日以降を毎日出力。Layer① は 24/25 共通 1 ジョブで 1 本を採用（判定は 02 STEP20）</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6022,7 @@
       </c>
       <c r="E17" s="167" t="inlineStr">
         <is>
-          <t>当日と昨日の翌日以降（*_YYYYMMDDhhmmss）をプルし、判定のうえ 1 本を発注IFへ変換して自動発注GCSへ SIREJAN_RCMDORDER_LAST_YYYYMMDDhhmmss として置く</t>
+          <t>当日と昨日の翌日以降をプル。1 本を発注IFへ変換し、自動発注GCSへ SIREJAN_RCMDORDER_LAST_YYYYMMDDhhmmss</t>
         </is>
       </c>
       <c r="F17" s="167" t="inlineStr">
@@ -6059,7 +6076,7 @@
       </c>
       <c r="E19" s="167" t="inlineStr">
         <is>
-          <t>DataSpider が Sinops から翌日以降勧告を処理し連携用GCSへ subkankoku_YYYYMMDDhhmmss.txt として出す。Layer① は 24 と共通ジョブ。OrdreSV へは送らない</t>
+          <t>Sinops → 連携用GCS。subkankoku_YYYYMMDDhhmmss.gz。完了印は subkankoku.end。Layer① は 24 と共通ジョブ。OrdreSV へは出さない</t>
         </is>
       </c>
       <c r="F19" s="167" t="inlineStr">
@@ -6155,7 +6172,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="B2" s="150" t="inlineStr">
         <is>
-          <t>下図：復路 Data Flow（詳細はノード定義表）。出典 draw.io 同梱。</t>
+          <t>復路。ノード定義は下表。図は draw.io</t>
         </is>
       </c>
     </row>
@@ -6347,7 +6364,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>図の各箱に対応。IP・正式ホストは未確定を TBD-DF-xx とし、09 シートと同一IDで管理。本機は Cloud Run Jobs。永続ディスクは持たない。</t>
+          <t>各箱の Server／IP／テーブル／ファイル。未確定は TBD-DF-xx（09 と同一）。Cloud Run Jobs。永続ディスクなし</t>
         </is>
       </c>
     </row>
@@ -6468,12 +6485,12 @@
       </c>
       <c r="G49" s="172" t="inlineStr">
         <is>
-          <t>出力物理: kankoku_YYYYMMDDhhmmss.txt／subkankoku_YYYYMMDDhhmmss.txt（論理は .txt）</t>
+          <t>出力物理: kankoku_YYYYMMDDhhmmss.gz／subkankoku_YYYYMMDDhhmmss.gz（論理は .txt）</t>
         </is>
       </c>
       <c r="H49" s="172" t="inlineStr">
         <is>
-          <t>毎日2ファイル。物理名にタイムスタンプ必須。採用判定・型変換はしない（Layer①）</t>
+          <t>毎日 gz 2本。各 gz の後に空の kankoku.end / subkankoku.end。採用判定・型変換はしない（Layer①）</t>
         </is>
       </c>
     </row>
@@ -6511,7 +6528,7 @@
       </c>
       <c r="G50" s="172" t="inlineStr">
         <is>
-          <t>kankoku_YYYYMMDDhhmmss.txt / subkankoku_YYYYMMDDhhmmss.txt</t>
+          <t>kankoku_YYYYMMDDhhmmss.gz / subkankoku_YYYYMMDDhhmmss.gz</t>
         </is>
       </c>
       <c r="H50" s="172" t="inlineStr">
@@ -6556,7 +6573,7 @@
       </c>
       <c r="G51" s="172" t="inlineStr">
         <is>
-          <t>IN: 代替採用時は昨日の subkankoku_YYYYMMDDhhmmss.txt
+          <t>IN: 代替採用時は昨日の subkankoku_YYYYMMDDhhmmss.gz
 （通常は当日 kankoku_*。判定は共通Job）
 OUT: SIREJAN_RCMDORDER_LAST_YYYYMMDDhhmmss（7項目）</t>
         </is>
@@ -6668,7 +6685,7 @@
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="173" t="inlineStr">
         <is>
-          <t>① Sinops → ② DataSpider(L3) → ③ 連携用GCS（kankoku_* / subkankoku_* を毎日配置・末尾タイムスタンプ）</t>
+          <t>① Sinops → ② DataSpider(L3) → ③ 連携用GCS（kankoku_*.gz / subkankoku_*.gz の後に .end）</t>
         </is>
       </c>
     </row>
@@ -6715,11 +6732,7 @@
       <c r="H59" s="185" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="169" t="inlineStr">
-        <is>
-          <t>■ 必須記載ルール（以降のIFも同じ）</t>
-        </is>
-      </c>
+      <c r="A61" s="169" t="n"/>
       <c r="B61" s="170" t="n"/>
       <c r="C61" s="170" t="n"/>
       <c r="D61" s="170" t="n"/>
@@ -6729,32 +6742,16 @@
       <c r="H61" s="170" t="n"/>
     </row>
     <row r="62" ht="36" customHeight="1">
-      <c r="A62" s="173" t="inlineStr">
-        <is>
-          <t>1. 図の箱ごと必ず埋める: Server名（またはマネージドサービス名）／IPまたは接続先／テーブル名／ファイル名</t>
-        </is>
-      </c>
+      <c r="A62" s="173" t="n"/>
     </row>
     <row r="63" ht="36" customHeight="1">
-      <c r="A63" s="173" t="inlineStr">
-        <is>
-          <t>2. マネージドサービス（GCS・Cloud Run）でIPが無い場合は「—」とし、接続経路（NAT/PSC等）を備考または TBD に書く</t>
-        </is>
-      </c>
+      <c r="A63" s="173" t="n"/>
     </row>
     <row r="64" ht="36" customHeight="1">
-      <c r="A64" s="173" t="inlineStr">
-        <is>
-          <t>3. 未確定は空欄禁止。TBD-DF-xx を採番し 09_確認事項・前提 に起票</t>
-        </is>
-      </c>
+      <c r="A64" s="173" t="n"/>
     </row>
     <row r="65" ht="36" customHeight="1">
-      <c r="A65" s="173" t="inlineStr">
-        <is>
-          <t>4. Layer② 対象外IFでも、経路上に出るノードは省略しない</t>
-        </is>
-      </c>
+      <c r="A65" s="173" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -6808,7 +6805,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="B3" s="173" t="inlineStr">
         <is>
-          <t>方針(2026-09-21): 型変換・フィールド選別・コード変換・編集は本 Layer① で実施。DSS 側では行わない。</t>
+          <t>2026-09-21: 型変換・選別・コード変換・編集は Layer①。DSS は全フィールド通過</t>
         </is>
       </c>
     </row>
@@ -6831,7 +6828,7 @@
       </c>
       <c r="C6" s="172" t="inlineStr">
         <is>
-          <t>連携用GCS上の当日（kankoku_*）と昨日の翌日以降（subkankoku_*）をプルし、採用判定のうえ 1 本だけ SIREJAN_RCMDORDER_LAST 7項目へ変換して TRIAL 自動発注GCSへ SIREJAN_RCMDORDER_LAST_YYYYMMDDhhmmss としてアップロードする。Layer① は 24/25 共通 1 ジョブ。後勝ちで 2 本重ねない</t>
+          <t>当日 kankoku_* と昨日の subkankoku_* をプル。STEP20 で 1 本を採用し、SIREJAN_RCMDORDER_LAST（7項目）へ変換。自動発注GCSへ SIREJAN_RCMDORDER_LAST_YYYYMMDDhhmmss。24/25 共通 1 ジョブ。2本は重ねない</t>
         </is>
       </c>
       <c r="D6" s="184" t="n"/>
@@ -6846,7 +6843,7 @@
       </c>
       <c r="C7" s="172" t="inlineStr">
         <is>
-          <t>連携用GCS（DSS配置）。当日 kankoku_YYYYMMDDhhmmss.txt（論理 kankoku.txt／Sinops-24）および昨日の subkankoku_YYYYMMDDhhmmss.txt（論理 subkankoku.txt／Sinops-25）</t>
+          <t>連携用GCS（DSS配置）。当日 kankoku_YYYYMMDDhhmmss.gz（論理 kankoku.txt）および昨日の subkankoku_YYYYMMDDhhmmss.gz（論理 subkankoku.txt）。完了印は空の kankoku.end / subkankoku.end</t>
         </is>
       </c>
       <c r="D7" s="184" t="n"/>
@@ -6860,7 +6857,7 @@
       </c>
       <c r="C8" s="172" t="inlineStr">
         <is>
-          <t>STEP20 で採用判定。当日が指定時刻（TBD-19、例 6:00）までに作成済なら当日。障害または未作成なら昨日の翌日以降。両方は採用しない</t>
+          <t>STEP20。指定時刻（TBD-19、例 6:00）までに当日作成済 → 当日。障害または未作成 → 昨日の翌日以降。2本は重ねない</t>
         </is>
       </c>
       <c r="D8" s="184" t="n"/>
@@ -6975,7 +6972,7 @@
       </c>
       <c r="C16" s="172" t="inlineStr">
         <is>
-          <t>連携用GCSから当日勧告と昨日の翌日以降勧告をプルし、クラウド機へステージング</t>
+          <t>kankoku.end / subkankoku.end を確認してから gz を取得・展開し、クラウド機へステージング</t>
         </is>
       </c>
       <c r="D16" s="172" t="inlineStr">
@@ -7060,7 +7057,7 @@
       </c>
       <c r="F18" s="172" t="inlineStr">
         <is>
-          <t>必須項目欠落・桁超過は ER-005。TBD項目は変換せず設計書の TBD に従う</t>
+          <t>必須項目欠落・桁超過は ER-005。未確定項目は TBD のまま</t>
         </is>
       </c>
       <c r="G18" s="172" t="inlineStr">
@@ -7499,18 +7496,10 @@
     </row>
     <row r="27" ht="18" customHeight="1"/>
     <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="173" t="inlineStr">
-        <is>
-          <t>※ STEPは10刻みで採番します。後から処理を挿入できるようにするためです。</t>
-        </is>
-      </c>
+      <c r="B28" s="173" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="173" t="inlineStr">
-        <is>
-          <t>※ 処理フローが複雑な場合は、別途フロー図（SVG/PowerPoint）を作成し、本シートに格納先を記載してください。</t>
-        </is>
-      </c>
+      <c r="B29" s="173" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7557,7 +7546,7 @@
     <row r="3" ht="42" customHeight="1">
       <c r="B3" s="173" t="inlineStr">
         <is>
-          <t>方針(2026-09-21): DataSpider は型変換・フィールド選別をしない（全フィールド通過）。型変換・選別・コード変換・編集は Layer①。</t>
+          <t>全フィールド通過。型変換・選別・編集は Layer①</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7569,7 @@
       </c>
       <c r="C6" s="172" t="inlineStr">
         <is>
-          <t>連携用GCS（TRIAL MD基幹への最終着地は自動発注転送。DSSはOrdreSVへ直送しない）</t>
+          <t>連携用GCSへ gz と空の .end。OrdreSV 直送なし。自動発注GCSは gz ではない</t>
         </is>
       </c>
       <c r="D6" s="184" t="n"/>
@@ -7594,7 +7583,7 @@
       </c>
       <c r="C7" s="172" t="inlineStr">
         <is>
-          <t>Sinops-25 翌日以降勧告。論理 subkankoku.txt。連携用GCS物理名 subkankoku_YYYYMMDDhhmmss.txt。毎日作成。Layer① 共通ジョブの代替入力（昨日分が当日の代わり）</t>
+          <t>Sinops-25 翌日以降勧告。論理 subkankoku.txt。連携用GCS物理名 subkankoku_YYYYMMDDhhmmss.gz。毎日作成。Layer① 共通ジョブの代替入力（昨日分が当日の代わり）</t>
         </is>
       </c>
       <c r="D7" s="184" t="n"/>
@@ -7724,7 +7713,7 @@
       </c>
       <c r="C15" s="172" t="inlineStr">
         <is>
-          <t>連携用GCSへ配置（物理名末尾 _YYYYMMDDhhmmss 必須）</t>
+          <t>連携用GCSへ gz を置く。続けて空の subkankoku.end</t>
         </is>
       </c>
       <c r="D15" s="172" t="inlineStr">
@@ -7846,18 +7835,10 @@
     </row>
     <row r="28" ht="18" customHeight="1"/>
     <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="173" t="inlineStr">
-        <is>
-          <t>※ STEPは10刻みで採番します。後から処理を挿入できるようにするためです。</t>
-        </is>
-      </c>
+      <c r="B29" s="173" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="173" t="inlineStr">
-        <is>
-          <t>※ 処理フローが複雑な場合は、別途フロー図（SVG/PowerPoint）を作成し、本シートに格納先を記載してください。</t>
-        </is>
-      </c>
+      <c r="B30" s="173" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7906,21 +7887,17 @@
     <row r="1" ht="24" customHeight="1">
       <c r="B1" s="161" t="inlineStr">
         <is>
-          <t>5. 項目マッピング — Layer①（型変換・選別・編集）</t>
+          <t>5. 項目マッピング（Layer①）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
-      <c r="B2" s="176" t="inlineStr">
-        <is>
-          <t>本設計書の中核です。Phase1のデータ項目比較・GAP一覧の結果をここに落とし込みます</t>
-        </is>
-      </c>
+      <c r="B2" s="176" t="n"/>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="B3" s="177" t="inlineStr">
         <is>
-          <t>方針(2026-09-21): **型変換・フィールド選別・コード変換・編集は本シート（Layer①）に書く。Layer②／③ は全フィールド通過のみ。**</t>
+          <t>型変換・選別・コード変換・編集</t>
         </is>
       </c>
       <c r="C3" s="184" t="n"/>
@@ -8108,7 +8085,7 @@
       </c>
       <c r="P7" s="172" t="inlineStr">
         <is>
-          <t>店CDの紐付けは西友（Sinops）とTRIALのマスタ統合で解決。本IFは6→4切捨て等の独自変換をしない。桁は統合作業に追随 TBD-01</t>
+          <t>マスタ統合後の店CD。6→4 の独自切捨てなし。桁は統合後 TBD-01</t>
         </is>
       </c>
       <c r="Q7" s="172" t="inlineStr">
@@ -8199,7 +8176,7 @@
       </c>
       <c r="P8" s="172" t="inlineStr">
         <is>
-          <t>商品の紐付けはマスタ統合で解決。本IFは独自の仕入JAN変換をしない。SireJANは統合後の商品コード。先頭ゼロ保持</t>
+          <t>統合後の商品コード。独自の仕入JAN変換なし。先頭ゼロ保持</t>
         </is>
       </c>
       <c r="Q8" s="172" t="inlineStr">
@@ -8373,7 +8350,7 @@
       </c>
       <c r="P10" s="148" t="inlineStr">
         <is>
-          <t>仕入先マスタも西友（Sinops）とTRIALで統合。本IFは9→8切捨て等の独自変換をしない。桁は統合作業に追随 TBD-08</t>
+          <t>マスタ統合後の仕入先。9→8 の独自切捨てなし。桁は統合後 TBD-08</t>
         </is>
       </c>
       <c r="Q10" s="148" t="inlineStr">
@@ -9609,14 +9586,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="B1" s="161" t="inlineStr">
         <is>
-          <t>5. 項目マッピング — Layer②（GCS→DWH Intake）</t>
+          <t>5. 項目マッピング（Layer②）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="B2" s="176" t="inlineStr">
         <is>
-          <t>方針: DataSpider Layer② は **全フィールド Intake**。型変換・フィールド選別はしない。本IFで Layer② が無い場合は「対象外」と明記する。</t>
+          <t>対象外。Intake しない</t>
         </is>
       </c>
     </row>
@@ -9629,11 +9606,7 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="173" t="inlineStr">
-        <is>
-          <t>（マスタIFのとき）受信先＝DWH Intake テーブル／送信元＝連携用GCSファイル。区分はすべて「直連携（全項目通過）」。</t>
-        </is>
-      </c>
+      <c r="B5" s="173" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1"/>
     <row r="7" ht="24" customHeight="1">
@@ -9752,21 +9725,21 @@
     <row r="1" ht="24" customHeight="1">
       <c r="B1" s="161" t="inlineStr">
         <is>
-          <t>5. 項目マッピング — Layer③（Sinops → 連携用GCS）</t>
+          <t>5. 項目マッピング（Layer③）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="40" customHeight="1">
       <c r="B2" s="176" t="inlineStr">
         <is>
-          <t>方針: DataSpider Layer③ は **全フィールド転送**。型変換・項目選別・コード編集はしない。送信元 Sinops と受信先連携用GCSは同一項目を直通。GCS物理名は subkankoku_YYYYMMDDhhmmss.txt（論理 subkankoku.txt）。</t>
+          <t>全フィールド転送。物理名 subkankoku_YYYYMMDDhhmmss.gz（論理 subkankoku.txt）。完了印は空の subkankoku.end</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="B3" s="173" t="inlineStr">
         <is>
-          <t>マッピング区分はすべて「直連携（全項目通過）」。変換・選別は 05_L① と 02_Layer① に書く。</t>
+          <t>区分は直連携（全項目通過）</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9827,7 @@
       </c>
       <c r="C6" s="152" t="inlineStr">
         <is>
-          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.txt（論理 subkankoku.txt）</t>
+          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.gz（論理 subkankoku.txt）</t>
         </is>
       </c>
       <c r="D6" s="152" t="inlineStr">
@@ -9917,11 +9890,7 @@
           <t>直連携（全項目通過）</t>
         </is>
       </c>
-      <c r="P6" s="152" t="inlineStr">
-        <is>
-          <t>DSSで型変換・選別しない</t>
-        </is>
-      </c>
+      <c r="P6" s="152" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="152" t="n">
@@ -9929,7 +9898,7 @@
       </c>
       <c r="C7" s="152" t="inlineStr">
         <is>
-          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.txt（論理 subkankoku.txt）</t>
+          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.gz（論理 subkankoku.txt）</t>
         </is>
       </c>
       <c r="D7" s="152" t="inlineStr">
@@ -9992,11 +9961,7 @@
           <t>直連携（全項目通過）</t>
         </is>
       </c>
-      <c r="P7" s="152" t="inlineStr">
-        <is>
-          <t>DSSで型変換・選別しない</t>
-        </is>
-      </c>
+      <c r="P7" s="152" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="B8" s="152" t="n">
@@ -10004,7 +9969,7 @@
       </c>
       <c r="C8" s="152" t="inlineStr">
         <is>
-          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.txt（論理 subkankoku.txt）</t>
+          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.gz（論理 subkankoku.txt）</t>
         </is>
       </c>
       <c r="D8" s="152" t="inlineStr">
@@ -10067,11 +10032,7 @@
           <t>直連携（全項目通過）</t>
         </is>
       </c>
-      <c r="P8" s="152" t="inlineStr">
-        <is>
-          <t>DSSで型変換・選別しない</t>
-        </is>
-      </c>
+      <c r="P8" s="152" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="B9" s="152" t="n">
@@ -10079,7 +10040,7 @@
       </c>
       <c r="C9" s="152" t="inlineStr">
         <is>
-          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.txt（論理 subkankoku.txt）</t>
+          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.gz（論理 subkankoku.txt）</t>
         </is>
       </c>
       <c r="D9" s="152" t="inlineStr">
@@ -10142,11 +10103,7 @@
           <t>直連携（全項目通過）</t>
         </is>
       </c>
-      <c r="P9" s="152" t="inlineStr">
-        <is>
-          <t>DSSで型変換・選別しない</t>
-        </is>
-      </c>
+      <c r="P9" s="152" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="B10" s="152" t="n">
@@ -10154,7 +10111,7 @@
       </c>
       <c r="C10" s="152" t="inlineStr">
         <is>
-          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.txt（論理 subkankoku.txt）</t>
+          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.gz（論理 subkankoku.txt）</t>
         </is>
       </c>
       <c r="D10" s="152" t="inlineStr">
@@ -10217,11 +10174,7 @@
           <t>直連携（全項目通過）</t>
         </is>
       </c>
-      <c r="P10" s="152" t="inlineStr">
-        <is>
-          <t>DSSで型変換・選別しない</t>
-        </is>
-      </c>
+      <c r="P10" s="152" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="B11" s="152" t="n">
@@ -10229,7 +10182,7 @@
       </c>
       <c r="C11" s="152" t="inlineStr">
         <is>
-          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.txt（論理 subkankoku.txt）</t>
+          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.gz（論理 subkankoku.txt）</t>
         </is>
       </c>
       <c r="D11" s="152" t="inlineStr">
@@ -10292,11 +10245,7 @@
           <t>直連携（全項目通過）</t>
         </is>
       </c>
-      <c r="P11" s="152" t="inlineStr">
-        <is>
-          <t>DSSで型変換・選別しない</t>
-        </is>
-      </c>
+      <c r="P11" s="152" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="B12" s="152" t="n">
@@ -10304,7 +10253,7 @@
       </c>
       <c r="C12" s="152" t="inlineStr">
         <is>
-          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.txt（論理 subkankoku.txt）</t>
+          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.gz（論理 subkankoku.txt）</t>
         </is>
       </c>
       <c r="D12" s="152" t="inlineStr">
@@ -10367,11 +10316,7 @@
           <t>直連携（全項目通過）</t>
         </is>
       </c>
-      <c r="P12" s="152" t="inlineStr">
-        <is>
-          <t>DSSで型変換・選別しない</t>
-        </is>
-      </c>
+      <c r="P12" s="152" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="152" t="n">
@@ -10379,7 +10324,7 @@
       </c>
       <c r="C13" s="152" t="inlineStr">
         <is>
-          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.txt（論理 subkankoku.txt）</t>
+          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.gz（論理 subkankoku.txt）</t>
         </is>
       </c>
       <c r="D13" s="152" t="inlineStr">
@@ -10442,11 +10387,7 @@
           <t>直連携（全項目通過）</t>
         </is>
       </c>
-      <c r="P13" s="152" t="inlineStr">
-        <is>
-          <t>DSSで型変換・選別しない</t>
-        </is>
-      </c>
+      <c r="P13" s="152" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="B14" s="152" t="n">
@@ -10454,7 +10395,7 @@
       </c>
       <c r="C14" s="152" t="inlineStr">
         <is>
-          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.txt（論理 subkankoku.txt）</t>
+          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.gz（論理 subkankoku.txt）</t>
         </is>
       </c>
       <c r="D14" s="152" t="inlineStr">
@@ -10517,11 +10458,7 @@
           <t>直連携（全項目通過）</t>
         </is>
       </c>
-      <c r="P14" s="152" t="inlineStr">
-        <is>
-          <t>DSSで型変換・選別しない</t>
-        </is>
-      </c>
+      <c r="P14" s="152" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="B15" s="152" t="n">
@@ -10529,7 +10466,7 @@
       </c>
       <c r="C15" s="152" t="inlineStr">
         <is>
-          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.txt（論理 subkankoku.txt）</t>
+          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.gz（論理 subkankoku.txt）</t>
         </is>
       </c>
       <c r="D15" s="152" t="inlineStr">
@@ -10592,11 +10529,7 @@
           <t>直連携（全項目通過）</t>
         </is>
       </c>
-      <c r="P15" s="152" t="inlineStr">
-        <is>
-          <t>DSSで型変換・選別しない</t>
-        </is>
-      </c>
+      <c r="P15" s="152" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="B16" s="152" t="n">
@@ -10604,7 +10537,7 @@
       </c>
       <c r="C16" s="152" t="inlineStr">
         <is>
-          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.txt（論理 subkankoku.txt）</t>
+          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.gz（論理 subkankoku.txt）</t>
         </is>
       </c>
       <c r="D16" s="152" t="inlineStr">
@@ -10667,11 +10600,7 @@
           <t>直連携（全項目通過）</t>
         </is>
       </c>
-      <c r="P16" s="152" t="inlineStr">
-        <is>
-          <t>DSSで型変換・選別しない</t>
-        </is>
-      </c>
+      <c r="P16" s="152" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="B17" s="152" t="n">
@@ -10679,7 +10608,7 @@
       </c>
       <c r="C17" s="152" t="inlineStr">
         <is>
-          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.txt（論理 subkankoku.txt）</t>
+          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.gz（論理 subkankoku.txt）</t>
         </is>
       </c>
       <c r="D17" s="152" t="inlineStr">
@@ -10742,11 +10671,7 @@
           <t>直連携（全項目通過）</t>
         </is>
       </c>
-      <c r="P17" s="152" t="inlineStr">
-        <is>
-          <t>DSSで型変換・選別しない</t>
-        </is>
-      </c>
+      <c r="P17" s="152" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="B18" s="152" t="n">
@@ -10754,7 +10679,7 @@
       </c>
       <c r="C18" s="152" t="inlineStr">
         <is>
-          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.txt（論理 subkankoku.txt）</t>
+          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.gz（論理 subkankoku.txt）</t>
         </is>
       </c>
       <c r="D18" s="152" t="inlineStr">
@@ -10817,11 +10742,7 @@
           <t>直連携（全項目通過）</t>
         </is>
       </c>
-      <c r="P18" s="152" t="inlineStr">
-        <is>
-          <t>DSSで型変換・選別しない</t>
-        </is>
-      </c>
+      <c r="P18" s="152" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="B19" s="152" t="n">
@@ -10829,7 +10750,7 @@
       </c>
       <c r="C19" s="152" t="inlineStr">
         <is>
-          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.txt（論理 subkankoku.txt）</t>
+          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.gz（論理 subkankoku.txt）</t>
         </is>
       </c>
       <c r="D19" s="152" t="inlineStr">
@@ -10892,11 +10813,7 @@
           <t>直連携（全項目通過）</t>
         </is>
       </c>
-      <c r="P19" s="152" t="inlineStr">
-        <is>
-          <t>DSSで型変換・選別しない</t>
-        </is>
-      </c>
+      <c r="P19" s="152" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="B20" s="152" t="n">
@@ -10904,7 +10821,7 @@
       </c>
       <c r="C20" s="152" t="inlineStr">
         <is>
-          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.txt（論理 subkankoku.txt）</t>
+          <t>連携用GCS / subkankoku_YYYYMMDDhhmmss.gz（論理 subkankoku.txt）</t>
         </is>
       </c>
       <c r="D20" s="152" t="inlineStr">
@@ -10967,11 +10884,7 @@
           <t>直連携（全項目通過）</t>
         </is>
       </c>
-      <c r="P20" s="152" t="inlineStr">
-        <is>
-          <t>DSSで型変換・選別しない</t>
-        </is>
-      </c>
+      <c r="P20" s="152" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/PMI/Sinops/phase2-detail-design/DD/Sinops_IFレイアウト_発注勧告翌日以降.xlsx
+++ b/PMI/Sinops/phase2-detail-design/DD/Sinops_IFレイアウト_発注勧告翌日以降.xlsx
@@ -4456,7 +4456,7 @@
       </c>
       <c r="C13" s="172" t="inlineStr">
         <is>
-          <t>Layer① STEP20 採用判定</t>
+          <t>Layer① STEP40 採用判定</t>
         </is>
       </c>
       <c r="D13" s="172" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="F13" s="172" t="inlineStr">
         <is>
-          <t>当日を不採用とし、昨日の翌日以降を 1 本として採用して STEP30 へ</t>
+          <t>当日を不採用とし、昨日の翌日以降を 1 本として採用して STEP50 へ</t>
         </is>
       </c>
       <c r="G13" s="172" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="E17" s="148" t="inlineStr">
         <is>
-          <t>02 STEP20</t>
+          <t>02 STEP40</t>
         </is>
       </c>
       <c r="F17" s="148" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="I18" s="148" t="inlineStr">
         <is>
-          <t>Layer① は 24/25 共通 1 ジョブ。STEP20 で 1 本採用。Layer③ は kankoku_* と subkankoku_* を毎日出力。締切は TBD-19</t>
+          <t>Layer① は 24/25 共通 1 ジョブ。STEP40 で 1 本採用。Layer③ は kankoku_* と subkankoku_* を毎日出力。締切は TBD-19</t>
         </is>
       </c>
       <c r="J18" s="148" t="inlineStr">
@@ -5824,7 +5824,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="B2" s="165" t="inlineStr">
         <is>
-          <t>Layer③ は当日・翌日以降を毎日出力。Layer① は 24/25 共通 1 ジョブで 1 本を採用（判定は 02 STEP20）</t>
+          <t>Layer③ は当日・翌日以降を毎日出力。Layer① は 24/25 共通 1 ジョブで 1 本を採用（判定は 02 STEP40）</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H32"/>
+  <dimension ref="B1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="C6" s="172" t="inlineStr">
         <is>
-          <t>当日 kankoku_* と昨日の subkankoku_* をプル。STEP20 で 1 本を採用し、SIREJAN_RCMDORDER_LAST（7項目）へ変換。自動発注GCSへ SIREJAN_RCMDORDER_LAST_YYYYMMDDhhmmss。24/25 共通 1 ジョブ。2本は重ねない</t>
+          <t>当日 kankoku_* と昨日の subkankoku_* をプル。STEP40 で 1 本を採用し、SIREJAN_RCMDORDER_LAST（7項目）へ変換。自動発注GCSへ SIREJAN_RCMDORDER_LAST_YYYYMMDDhhmmss。24/25 共通 1 ジョブ。2本は重ねない</t>
         </is>
       </c>
       <c r="D6" s="184" t="n"/>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C8" s="172" t="inlineStr">
         <is>
-          <t>STEP20。指定時刻（TBD-19、例 6:00）までに当日作成済 → 当日。障害または未作成 → 昨日の翌日以降。2本は重ねない</t>
+          <t>STEP40。指定時刻（TBD-19、例 6:00）までに当日作成済 → 当日。障害または未作成 → 昨日の翌日以降。2本は重ねない</t>
         </is>
       </c>
       <c r="D8" s="184" t="n"/>
@@ -6966,233 +6966,548 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="B16" s="172" t="n">
-        <v>10</v>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="172" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="C16" s="172" t="inlineStr">
         <is>
-          <t>kankoku.end / subkankoku.end を確認してから gz を取得・展開し、クラウド機へステージング</t>
+          <t>.end を確認</t>
         </is>
       </c>
       <c r="D16" s="172" t="inlineStr">
         <is>
-          <t>gs://ods-seiyu-prod/{TBD-05}/ 当日 ＋ 昨日の翌日以降</t>
+          <t>kankoku.end / subkankoku.end</t>
         </is>
       </c>
       <c r="E16" s="172" t="inlineStr">
         <is>
-          <t>本機ステージング（最大 2 ファイル）</t>
+          <t>有無</t>
         </is>
       </c>
       <c r="F16" s="172" t="inlineStr">
         <is>
-          <t>両方取れない場合は ER-004。当日0件は判定へ（ER-012）</t>
+          <t>両方無しは ER-004</t>
         </is>
       </c>
       <c r="G16" s="172" t="inlineStr">
         <is>
-          <t>Hinemos 起動 Layer①（24/25 共通）</t>
+          <t>空ファイル</t>
         </is>
       </c>
       <c r="H16" s="173" t="inlineStr">
         <is>
-          <t>共通 1 ジョブ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="84" customHeight="1">
-      <c r="B17" s="172" t="n">
-        <v>20</v>
+          <t>24/25 共通</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="B17" s="172" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C17" s="172" t="inlineStr">
         <is>
-          <t>採用判定。当日ファイルが指定時刻（TBD-19、例 6:00）までに作成済 → 当日を採用。障害、または当日未作成 → 昨日作成の翌日以降を採用。2 本を後勝ちで重ねない</t>
+          <t>gz を取得</t>
         </is>
       </c>
       <c r="D17" s="172" t="inlineStr">
         <is>
-          <t>ステージング上の当日 ＋ 昨日の翌日以降</t>
+          <t>連携用GCS</t>
         </is>
       </c>
       <c r="E17" s="172" t="inlineStr">
         <is>
-          <t>採用する 1 ファイル</t>
+          <t>gz（最大2）</t>
         </is>
       </c>
       <c r="F17" s="172" t="inlineStr">
         <is>
-          <t>当日未作成・障害は ER-012 で昨日分を採用。昨日分も無ければ中断</t>
+          <t>失敗は ER-004</t>
         </is>
       </c>
       <c r="G17" s="172" t="inlineStr">
         <is>
-          <t>TBD-13/19。後勝ちしない</t>
-        </is>
-      </c>
-      <c r="H17" s="173" t="inlineStr">
-        <is>
-          <t>判定は本機。自動発注側では選ばない</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="72" customHeight="1">
-      <c r="B18" s="172" t="n">
-        <v>30</v>
+          <t>当日 kankoku_*.gz と昨日 subkankoku_*.gz</t>
+        </is>
+      </c>
+      <c r="H17" s="173" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="B18" s="172" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="C18" s="172" t="inlineStr">
         <is>
-          <t>採用した 1 本を SIREJAN_RCMDORDER_LAST へ変換。数量は×1000しない。発注単位の整数倍であれば発注バラ数を直接設定（倍数に丸めない）。Ordertype は勧告ファイルの西友中分類（西友ライン＝部門）を部門CDとし、自動発注GCS JIHA.BUMON_ZONE（部門CD, ZONECD）→ JIHA.ZONE_LOGIC（ZONECD, 論理区分）。論理区分 01→0（非日配）、02→1（日配）、03→1（生鮮）。TRIAL 商品マスタは参照しない。</t>
+          <t>gz を展開</t>
         </is>
       </c>
       <c r="D18" s="172" t="inlineStr">
         <is>
-          <t>採用した 1 本（部門＝西友中分類／西友ライン）＋ JIHA.BUMON_ZONE / JIHA.ZONE_LOGIC（自動発注GCS）</t>
+          <t>gz</t>
         </is>
       </c>
       <c r="E18" s="172" t="inlineStr">
         <is>
-          <t>7項目ファイル 1 本</t>
-        </is>
-      </c>
-      <c r="F18" s="172" t="inlineStr">
-        <is>
-          <t>必須項目欠落・桁超過は ER-005。未確定項目は TBD のまま</t>
-        </is>
-      </c>
+          <t>ステージング</t>
+        </is>
+      </c>
+      <c r="F18" s="172" t="n"/>
       <c r="G18" s="172" t="inlineStr">
         <is>
-          <t>R01/R04/R06/R07 確定。部門は勧告ファイル。商品マスタは見ない。数量は発注単位の整数倍。店・仕入先・商品はマスタ統合に追随</t>
-        </is>
-      </c>
-      <c r="H18" s="173" t="inlineStr">
-        <is>
-          <t>変換対象は採用した 1 本のみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="21.75" customHeight="1">
-      <c r="B19" s="172" t="n">
-        <v>40</v>
+          <t>最大 2 ファイル</t>
+        </is>
+      </c>
+      <c r="H18" s="173" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="172" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="C19" s="172" t="inlineStr">
         <is>
-          <t>変換後ファイル（採用した 1 本）を TRIAL 自動発注GCSへアップロード</t>
+          <t>採用する 1 本を決める</t>
         </is>
       </c>
       <c r="D19" s="172" t="inlineStr">
         <is>
-          <t>7項目ファイル 1 本</t>
+          <t>ステージング</t>
         </is>
       </c>
       <c r="E19" s="172" t="inlineStr">
         <is>
+          <t>採用 1 本</t>
+        </is>
+      </c>
+      <c r="F19" s="172" t="inlineStr">
+        <is>
+          <t>当日無しは ER-012。昨日も無しは中断</t>
+        </is>
+      </c>
+      <c r="G19" s="172" t="inlineStr">
+        <is>
+          <t>締切 TBD-19（例 6:00）。2本は重ねない</t>
+        </is>
+      </c>
+      <c r="H19" s="173" t="inlineStr">
+        <is>
+          <t>判定は本機</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="172" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C20" s="172" t="inlineStr">
+        <is>
+          <t>店CDを統合マスタ後へ</t>
+        </is>
+      </c>
+      <c r="D20" s="172" t="inlineStr">
+        <is>
+          <t>採用 1 本</t>
+        </is>
+      </c>
+      <c r="E20" s="172" t="inlineStr">
+        <is>
+          <t>店舗CD</t>
+        </is>
+      </c>
+      <c r="F20" s="172" t="inlineStr">
+        <is>
+          <t>不一致は ER-005</t>
+        </is>
+      </c>
+      <c r="G20" s="172" t="inlineStr">
+        <is>
+          <t>切捨てなし。TBD-01</t>
+        </is>
+      </c>
+      <c r="H20" s="173" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="172" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C21" s="172" t="inlineStr">
+        <is>
+          <t>商品CDを統合マスタ後へ</t>
+        </is>
+      </c>
+      <c r="D21" s="172" t="inlineStr">
+        <is>
+          <t>採用 1 本</t>
+        </is>
+      </c>
+      <c r="E21" s="172" t="inlineStr">
+        <is>
+          <t>仕入発注JAN</t>
+        </is>
+      </c>
+      <c r="F21" s="172" t="inlineStr">
+        <is>
+          <t>不一致は ER-005</t>
+        </is>
+      </c>
+      <c r="G21" s="172" t="inlineStr">
+        <is>
+          <t>独自変換なし</t>
+        </is>
+      </c>
+      <c r="H21" s="173" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="172" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="C22" s="172" t="inlineStr">
+        <is>
+          <t>仕入先CDを統合マスタ後へ</t>
+        </is>
+      </c>
+      <c r="D22" s="172" t="inlineStr">
+        <is>
+          <t>採用 1 本</t>
+        </is>
+      </c>
+      <c r="E22" s="172" t="inlineStr">
+        <is>
+          <t>ベンダーCD</t>
+        </is>
+      </c>
+      <c r="F22" s="172" t="inlineStr">
+        <is>
+          <t>不一致は ER-005</t>
+        </is>
+      </c>
+      <c r="G22" s="172" t="inlineStr">
+        <is>
+          <t>切捨てなし。TBD-08</t>
+        </is>
+      </c>
+      <c r="H22" s="173" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="172" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="C23" s="172" t="inlineStr">
+        <is>
+          <t>数量を設定</t>
+        </is>
+      </c>
+      <c r="D23" s="172" t="inlineStr">
+        <is>
+          <t>発注バラ数</t>
+        </is>
+      </c>
+      <c r="E23" s="172" t="inlineStr">
+        <is>
+          <t>推奨発注数量</t>
+        </is>
+      </c>
+      <c r="F23" s="172" t="inlineStr">
+        <is>
+          <t>整数倍でないは ER-005</t>
+        </is>
+      </c>
+      <c r="G23" s="172" t="inlineStr">
+        <is>
+          <t>×1000しない。丸めない</t>
+        </is>
+      </c>
+      <c r="H23" s="173" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="172" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="C24" s="172" t="inlineStr">
+        <is>
+          <t>納品日を移す</t>
+        </is>
+      </c>
+      <c r="D24" s="172" t="inlineStr">
+        <is>
+          <t>納品日</t>
+        </is>
+      </c>
+      <c r="E24" s="172" t="inlineStr">
+        <is>
+          <t>ShippingDate</t>
+        </is>
+      </c>
+      <c r="F24" s="172" t="n"/>
+      <c r="G24" s="172" t="inlineStr">
+        <is>
+          <t>yyyymmdd のまま</t>
+        </is>
+      </c>
+      <c r="H24" s="173" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="172" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C25" s="172" t="inlineStr">
+        <is>
+          <t>部門CDを取る</t>
+        </is>
+      </c>
+      <c r="D25" s="172" t="inlineStr">
+        <is>
+          <t>勧告ファイルの西友中分類</t>
+        </is>
+      </c>
+      <c r="E25" s="172" t="inlineStr">
+        <is>
+          <t>部門CD</t>
+        </is>
+      </c>
+      <c r="F25" s="172" t="n"/>
+      <c r="G25" s="172" t="inlineStr">
+        <is>
+          <t>西友ライン＝部門。商品マスタは見ない</t>
+        </is>
+      </c>
+      <c r="H25" s="173" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="172" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="C26" s="172" t="inlineStr">
+        <is>
+          <t>JIHA.BUMON_ZONE を引く</t>
+        </is>
+      </c>
+      <c r="D26" s="172" t="inlineStr">
+        <is>
+          <t>自動発注GCS / JIHA.BUMON_ZONE</t>
+        </is>
+      </c>
+      <c r="E26" s="172" t="inlineStr">
+        <is>
+          <t>ZONECD</t>
+        </is>
+      </c>
+      <c r="F26" s="172" t="inlineStr">
+        <is>
+          <t>部門CDが無いのは ER-007</t>
+        </is>
+      </c>
+      <c r="G26" s="172" t="inlineStr">
+        <is>
+          <t>キーは部門CD。参照のみ。書かない</t>
+        </is>
+      </c>
+      <c r="H26" s="173" t="inlineStr">
+        <is>
+          <t>自動発注GCS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="172" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C27" s="172" t="inlineStr">
+        <is>
+          <t>JIHA.ZONE_LOGIC を引く</t>
+        </is>
+      </c>
+      <c r="D27" s="172" t="inlineStr">
+        <is>
+          <t>自動発注GCS / JIHA.ZONE_LOGIC</t>
+        </is>
+      </c>
+      <c r="E27" s="172" t="inlineStr">
+        <is>
+          <t>論理区分</t>
+        </is>
+      </c>
+      <c r="F27" s="172" t="inlineStr">
+        <is>
+          <t>引けないは ER-007</t>
+        </is>
+      </c>
+      <c r="G27" s="172" t="inlineStr">
+        <is>
+          <t>キーは ZONECD。参照のみ。書かない</t>
+        </is>
+      </c>
+      <c r="H27" s="173" t="inlineStr">
+        <is>
+          <t>自動発注GCS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="172" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="C28" s="172" t="inlineStr">
+        <is>
+          <t>Ordertype を設定</t>
+        </is>
+      </c>
+      <c r="D28" s="172" t="inlineStr">
+        <is>
+          <t>論理区分</t>
+        </is>
+      </c>
+      <c r="E28" s="172" t="inlineStr">
+        <is>
+          <t>Ordertype</t>
+        </is>
+      </c>
+      <c r="F28" s="172" t="inlineStr">
+        <is>
+          <t>01/02/03 以外は ER-007</t>
+        </is>
+      </c>
+      <c r="G28" s="172" t="inlineStr">
+        <is>
+          <t>01→0、02→1、03→1</t>
+        </is>
+      </c>
+      <c r="H28" s="173" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="172" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C29" s="172" t="inlineStr">
+        <is>
+          <t>更新日を設定</t>
+        </is>
+      </c>
+      <c r="D29" s="172" t="inlineStr">
+        <is>
+          <t>発注日（候補）</t>
+        </is>
+      </c>
+      <c r="E29" s="172" t="inlineStr">
+        <is>
+          <t>更新日</t>
+        </is>
+      </c>
+      <c r="F29" s="172" t="n"/>
+      <c r="G29" s="172" t="inlineStr">
+        <is>
+          <t>TBD-10</t>
+        </is>
+      </c>
+      <c r="H29" s="173" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="172" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C30" s="172" t="inlineStr">
+        <is>
+          <t>SIREJAN を書く</t>
+        </is>
+      </c>
+      <c r="D30" s="172" t="inlineStr">
+        <is>
+          <t>7項目</t>
+        </is>
+      </c>
+      <c r="E30" s="172" t="inlineStr">
+        <is>
+          <t>1 ファイル</t>
+        </is>
+      </c>
+      <c r="F30" s="172" t="inlineStr">
+        <is>
+          <t>必須欠落は ER-005</t>
+        </is>
+      </c>
+      <c r="G30" s="172" t="inlineStr">
+        <is>
+          <t>gz ではない</t>
+        </is>
+      </c>
+      <c r="H30" s="173" t="inlineStr">
+        <is>
+          <t>SIREJAN_RCMDORDER_LAST_YYYYMMDDhhmmss</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="172" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C31" s="172" t="inlineStr">
+        <is>
+          <t>自動発注GCSへ置く</t>
+        </is>
+      </c>
+      <c r="D31" s="172" t="inlineStr">
+        <is>
+          <t>1 ファイル</t>
+        </is>
+      </c>
+      <c r="E31" s="172" t="inlineStr">
+        <is>
           <t>gs://{TBD-06}/</t>
         </is>
       </c>
-      <c r="F19" s="172" t="inlineStr">
-        <is>
-          <t>配置失敗は ER-006 で中断</t>
-        </is>
-      </c>
-      <c r="G19" s="172" t="inlineStr">
-        <is>
-          <t>OrdreSV へは既存自動発注転送。本STEPの外</t>
-        </is>
-      </c>
-      <c r="H19" s="173" t="inlineStr">
+      <c r="F31" s="172" t="inlineStr">
+        <is>
+          <t>失敗は ER-006</t>
+        </is>
+      </c>
+      <c r="G31" s="172" t="inlineStr">
+        <is>
+          <t>OrdreSV は本STEPの外</t>
+        </is>
+      </c>
+      <c r="H31" s="173" t="inlineStr">
         <is>
           <t>出力は常に 1 本</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="21.75" customHeight="1">
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="21.75" customHeight="1">
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="21.75" customHeight="1">
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-    </row>
-    <row r="23" ht="21.75" customHeight="1">
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="10" t="n"/>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="10" t="n"/>
-    </row>
-    <row r="24" ht="21.75" customHeight="1">
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
-    </row>
-    <row r="25" ht="21.75" customHeight="1">
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10" t="n"/>
-    </row>
-    <row r="26" ht="21.75" customHeight="1">
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="n"/>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="10" t="n"/>
-    </row>
-    <row r="27" ht="21.75" customHeight="1">
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="n"/>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="10" t="n"/>
-    </row>
-    <row r="28" ht="21.75" customHeight="1">
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="10" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1"/>
-    <row r="31" ht="18" customHeight="1">
-      <c r="B31" s="11" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="2" t="n"/>
     </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C11:E11"/>
@@ -7681,13 +7996,15 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="31.5" customHeight="1">
-      <c r="B14" s="172" t="n">
-        <v>10</v>
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="172" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="C14" s="172" t="inlineStr">
         <is>
-          <t>Sinops から翌日以降勧告を取得</t>
+          <t>翌日以降勧告を取得</t>
         </is>
       </c>
       <c r="D14" s="172" t="inlineStr">
@@ -7697,61 +8014,107 @@
       </c>
       <c r="E14" s="172" t="inlineStr">
         <is>
-          <t>DSS 作業領域</t>
+          <t>DSS作業領域</t>
         </is>
       </c>
       <c r="F14" s="172" t="inlineStr">
         <is>
-          <t>取得失敗は処理中断・通知</t>
-        </is>
-      </c>
-      <c r="G14" s="145" t="inlineStr"/>
-    </row>
-    <row r="15" ht="21.75" customHeight="1">
-      <c r="B15" s="172" t="n">
-        <v>20</v>
+          <t>失敗は中断・通知</t>
+        </is>
+      </c>
+      <c r="G14" s="145" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="172" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C15" s="172" t="inlineStr">
         <is>
-          <t>連携用GCSへ gz を置く。続けて空の subkankoku.end</t>
+          <t>gz にする</t>
         </is>
       </c>
       <c r="D15" s="172" t="inlineStr">
         <is>
-          <t>DSS 作業領域</t>
+          <t>DSS作業領域</t>
         </is>
       </c>
       <c r="E15" s="172" t="inlineStr">
         <is>
+          <t>subkankoku_YYYYMMDDhhmmss.gz</t>
+        </is>
+      </c>
+      <c r="F15" s="172" t="n"/>
+      <c r="G15" s="145" t="inlineStr">
+        <is>
+          <t>論理 subkankoku.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="172" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C16" s="172" t="inlineStr">
+        <is>
+          <t>gz を連携用GCSへ置く</t>
+        </is>
+      </c>
+      <c r="D16" s="172" t="inlineStr">
+        <is>
+          <t>gz</t>
+        </is>
+      </c>
+      <c r="E16" s="172" t="inlineStr">
+        <is>
           <t>gs://ods-seiyu-prod/{TBD-05}/</t>
         </is>
       </c>
-      <c r="F15" s="172" t="inlineStr">
-        <is>
-          <t>配置失敗は処理中断・通知</t>
-        </is>
-      </c>
-      <c r="G15" s="172" t="inlineStr">
-        <is>
-          <t>UTF-8。フォルダ名は西友 from_to_連番（TBD-05）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="21.75" customHeight="1">
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-    </row>
-    <row r="17" ht="21.75" customHeight="1">
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="10" t="n"/>
+      <c r="F16" s="172" t="inlineStr">
+        <is>
+          <t>失敗は中断・通知</t>
+        </is>
+      </c>
+      <c r="G16" s="145" t="inlineStr">
+        <is>
+          <t>from_to_連番（TBD-05）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="B17" s="172" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C17" s="172" t="inlineStr">
+        <is>
+          <t>空の subkankoku.end を置く</t>
+        </is>
+      </c>
+      <c r="D17" s="172" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="E17" s="172" t="inlineStr">
+        <is>
+          <t>subkankoku.end</t>
+        </is>
+      </c>
+      <c r="F17" s="172" t="inlineStr">
+        <is>
+          <t>失敗は中断・通知</t>
+        </is>
+      </c>
+      <c r="G17" s="145" t="inlineStr">
+        <is>
+          <t>gz の後</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="21.75" customHeight="1">
       <c r="B18" s="10" t="n"/>
